--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3218" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>Choctaw</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -435,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1584"/>
+  <dimension ref="A1:Q1584"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="24.140625" customWidth="1"/>
@@ -443,9 +449,11 @@
     <col min="12" max="12" width="19.42578125" customWidth="1"/>
     <col min="13" max="13" width="12.42578125" customWidth="1"/>
     <col min="14" max="14" width="53" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +499,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -509,7 +523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -529,7 +543,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -549,7 +563,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -569,7 +583,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -589,7 +603,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -609,7 +623,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -629,7 +643,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -649,7 +663,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -669,7 +683,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -689,7 +703,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -709,7 +723,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -729,7 +743,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -749,7 +763,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -769,7 +783,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Choctaw Newborn By Blood.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3218" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -106,10 +106,13 @@
     <t>Choctaw</t>
   </si>
   <si>
-    <t>Image Name</t>
+    <t>ImageBinary</t>
   </si>
   <si>
-    <t>Image Binary</t>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q1584"/>
+  <dimension ref="A1:R1584"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="24.140625" customWidth="1"/>
@@ -451,9 +454,10 @@
     <col min="14" max="14" width="53" customWidth="1"/>
     <col min="16" max="16" width="14.140625" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" customWidth="1"/>
+    <col min="18" max="18" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -500,13 +504,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q1" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -523,7 +530,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -543,7 +550,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -563,7 +570,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -583,7 +590,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -603,7 +610,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -623,7 +630,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -643,7 +650,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -663,7 +670,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -683,7 +690,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -703,7 +710,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -723,7 +730,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -743,7 +750,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -763,7 +770,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -783,7 +790,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 98</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
